--- a/artfynd/A 68939-2021 artfynd.xlsx
+++ b/artfynd/A 68939-2021 artfynd.xlsx
@@ -1543,10 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117413468</v>
+        <v>117413505</v>
       </c>
       <c r="B9" t="n">
-        <v>57691</v>
+        <v>57990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,20 +1555,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103037</v>
+        <v>103055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1578,30 +1578,30 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Solbacka, Vstm</t>
+          <t>Strömsnäsberget, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546577</v>
+        <v>546610</v>
       </c>
       <c r="R9" t="n">
-        <v>6582282</v>
+        <v>6582670</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Arboga stad</t>
+          <t>Arboga socken</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>05:17</t>
+          <t>05:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>05:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1667,10 +1667,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117413505</v>
+        <v>117413466</v>
       </c>
       <c r="B10" t="n">
-        <v>57990</v>
+        <v>57510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1679,53 +1679,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103055</v>
+        <v>102981</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Strömsnäsberget, Vstm</t>
+          <t>Solbacka, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546610</v>
+        <v>546577</v>
       </c>
       <c r="R10" t="n">
-        <v>6582670</v>
+        <v>6582282</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Arboga socken</t>
+          <t>Arboga stad</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>05:42</t>
+          <t>05:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>05:42</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1791,7 +1791,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117413487</v>
+        <v>117413470</v>
       </c>
       <c r="B11" t="n">
         <v>57990</v>
@@ -1839,17 +1839,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Harmossen, Vstm</t>
+          <t>Solbacka, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546507</v>
+        <v>546577</v>
       </c>
       <c r="R11" t="n">
-        <v>6582488</v>
+        <v>6582282</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Arboga socken</t>
+          <t>Arboga stad</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>05:28</t>
+          <t>05:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>05:34</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1915,10 +1915,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117413466</v>
+        <v>117413487</v>
       </c>
       <c r="B12" t="n">
-        <v>57510</v>
+        <v>57990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1927,53 +1927,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102981</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Solbacka, Vstm</t>
+          <t>Harmossen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546577</v>
+        <v>546507</v>
       </c>
       <c r="R12" t="n">
-        <v>6582282</v>
+        <v>6582488</v>
       </c>
       <c r="S12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Arboga stad</t>
+          <t>Arboga socken</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>05:17</t>
+          <t>05:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2039,10 +2039,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117413470</v>
+        <v>117413468</v>
       </c>
       <c r="B13" t="n">
-        <v>57990</v>
+        <v>57691</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2051,20 +2051,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>103037</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2074,14 +2074,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>

--- a/artfynd/A 68939-2021 artfynd.xlsx
+++ b/artfynd/A 68939-2021 artfynd.xlsx
@@ -2166,7 +2166,7 @@
         <v>117914573</v>
       </c>
       <c r="B14" t="n">
-        <v>57828</v>
+        <v>57829</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>117914557</v>
       </c>
       <c r="B15" t="n">
-        <v>57990</v>
+        <v>57991</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 68939-2021 artfynd.xlsx
+++ b/artfynd/A 68939-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116392654</v>
+        <v>116393225</v>
       </c>
       <c r="B2" t="n">
-        <v>58079</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,23 +712,23 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strömsnäsberget, Vstm</t>
+          <t>Harmossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546635</v>
+        <v>546637</v>
       </c>
       <c r="R2" t="n">
-        <v>6582660</v>
+        <v>6582326</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +747,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Arboga socken</t>
+          <t>Arboga stad</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -762,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,32 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116393082</v>
+        <v>117413466</v>
       </c>
       <c r="B3" t="n">
-        <v>58052</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58212</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>102981</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,30 +824,30 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Harmossen, Vstm</t>
+          <t>Solbacka, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546507</v>
+        <v>546577</v>
       </c>
       <c r="R3" t="n">
-        <v>6582488</v>
+        <v>6582282</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,27 +866,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Arboga socken</t>
+          <t>Arboga stad</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>05:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,16 +916,11 @@
         <v>116393079</v>
       </c>
       <c r="B4" t="n">
-        <v>57910</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1047,32 +1032,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116392653</v>
+        <v>117914573</v>
       </c>
       <c r="B5" t="n">
-        <v>58052</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1095,17 +1075,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strömsnäsberget, Vstm</t>
+          <t>Harmossen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546635</v>
+        <v>546443</v>
       </c>
       <c r="R5" t="n">
-        <v>6582660</v>
+        <v>6582528</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,15 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116393077</v>
+        <v>116392285</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,30 +1181,30 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Harmossen, Vstm</t>
+          <t>Strömsnäsberget, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546507</v>
+        <v>546441</v>
       </c>
       <c r="R6" t="n">
-        <v>6582488</v>
+        <v>6582820</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1258,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,15 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116393225</v>
+        <v>116392648</v>
       </c>
       <c r="B7" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,16 +1281,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100065</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1337,23 +1307,23 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Harmossen, Vstm</t>
+          <t>Strömsnäsberget, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546637</v>
+        <v>546635</v>
       </c>
       <c r="R7" t="n">
-        <v>6582326</v>
+        <v>6582660</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,7 +1342,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Arboga stad</t>
+          <t>Arboga socken</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1382,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1392,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,15 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116392648</v>
+        <v>116393077</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1419,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1467,17 +1432,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Strömsnäsberget, Vstm</t>
+          <t>Harmossen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546635</v>
+        <v>546507</v>
       </c>
       <c r="R8" t="n">
-        <v>6582660</v>
+        <v>6582488</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1506,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1516,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,37 +1508,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117413505</v>
+        <v>117413548</v>
       </c>
       <c r="B9" t="n">
-        <v>58079</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1585,7 +1545,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1595,13 +1555,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546610</v>
+        <v>546530</v>
       </c>
       <c r="R9" t="n">
-        <v>6582670</v>
+        <v>6582784</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1630,7 +1590,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>05:42</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1640,7 +1600,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>05:42</t>
+          <t>05:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1667,15 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117413466</v>
+        <v>117413468</v>
       </c>
       <c r="B10" t="n">
-        <v>57571</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,26 +1638,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102981</v>
+        <v>103037</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1791,37 +1746,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117413470</v>
+        <v>116392290</v>
       </c>
       <c r="B11" t="n">
-        <v>58079</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1833,23 +1783,23 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Solbacka, Vstm</t>
+          <t>Strömsnäsberget, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546577</v>
+        <v>546441</v>
       </c>
       <c r="R11" t="n">
-        <v>6582282</v>
+        <v>6582820</v>
       </c>
       <c r="S11" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1868,27 +1818,27 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Arboga stad</t>
+          <t>Arboga socken</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>05:17</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1915,37 +1865,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117413487</v>
+        <v>116392653</v>
       </c>
       <c r="B12" t="n">
-        <v>58079</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1957,23 +1902,23 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Harmossen, Vstm</t>
+          <t>Strömsnäsberget, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546507</v>
+        <v>546635</v>
       </c>
       <c r="R12" t="n">
-        <v>6582488</v>
+        <v>6582660</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1997,22 +1942,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>05:28</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>05:34</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2039,65 +1984,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117413468</v>
+        <v>116393082</v>
       </c>
       <c r="B13" t="n">
-        <v>57779</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103037</v>
+        <v>103044</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Solbacka, Vstm</t>
+          <t>Harmossen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546577</v>
+        <v>546507</v>
       </c>
       <c r="R13" t="n">
-        <v>6582282</v>
+        <v>6582488</v>
       </c>
       <c r="S13" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2116,27 +2056,27 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Arboga stad</t>
+          <t>Arboga socken</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>05:17</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2163,15 +2103,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117914557</v>
+        <v>116392654</v>
       </c>
       <c r="B14" t="n">
-        <v>58079</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2138,11 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2211,13 +2150,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546523</v>
+        <v>546635</v>
       </c>
       <c r="R14" t="n">
-        <v>6582704</v>
+        <v>6582660</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2241,22 +2180,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2283,37 +2222,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117914573</v>
+        <v>117413470</v>
       </c>
       <c r="B15" t="n">
-        <v>57910</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2325,23 +2259,23 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Harmossen, Vstm</t>
+          <t>Solbacka, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546443</v>
+        <v>546577</v>
       </c>
       <c r="R15" t="n">
-        <v>6582528</v>
+        <v>6582282</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2360,27 +2294,27 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Arboga socken</t>
+          <t>Arboga stad</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2404,6 +2338,716 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>117413487</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Harmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>546507</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6582488</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arboga socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>05:28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>117413505</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Strömsnäsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>546610</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6582670</v>
+      </c>
+      <c r="S17" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arboga socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>05:42</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>05:42</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>117914557</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Strömsnäsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>546523</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6582704</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arboga socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>05:53</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>116393226</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Harmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>546637</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6582326</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arboga stad</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>117413481</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Harmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>546507</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6582488</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arboga socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>05:28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>117914549</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Strömsnäsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>546523</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6582704</v>
+      </c>
+      <c r="S21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arboga socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>05:53</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 68939-2021 artfynd.xlsx
+++ b/artfynd/A 68939-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116393225</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117413466</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116393079</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117914573</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116392285</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1386,6 +1416,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116392648</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1505,6 +1540,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116393077</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1624,6 +1664,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117413548</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1743,6 +1788,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117413468</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1862,6 +1912,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116392290</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1981,6 +2036,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116392653</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2100,6 +2160,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116393082</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2219,6 +2284,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116392654</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2338,6 +2408,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117413470</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2457,6 +2532,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117413487</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2576,6 +2656,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117413505</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2691,6 +2776,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117914557</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2810,6 +2900,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116393226</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2929,6 +3024,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117413481</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3048,8 +3148,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117914549</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>